--- a/DateBase/orders/Nhat 48_2026-10-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-24.xlsx
@@ -518,7 +518,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-10-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -520,10 +520,96 @@
       <c r="A11" t="str">
         <v>3</v>
       </c>
+      <c r="C11" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F11" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>577_腊梅白_wax white_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>4</v>
+      </c>
+      <c r="C15" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>264_和弦_harmony_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -578,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0525103558150</v>
+        <v>052510355815402551281057100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-10-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-24.xlsx
@@ -606,6 +606,9 @@
       <c r="A21" t="str">
         <v>5</v>
       </c>
+      <c r="C21" t="str">
+        <v>264_和弦_harmony_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nhat 48_2026-10-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-24.xlsx
@@ -609,6 +609,9 @@
       <c r="C21" t="str">
         <v>264_和弦_harmony_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -667,7 +670,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>052510355815402551281057100</v>
+        <v>052510355815402551281057104</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-10-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -613,9 +613,180 @@
         <v>4</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>157_流沙_Quicksand_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>6</v>
+      </c>
+      <c r="C25" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F25" t="str">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>111_绣球紫_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F26" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F27" t="str">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>7</v>
+      </c>
+      <c r="C29" t="str">
+        <v>662_大丽花 白_undefined_undefined_5stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>388_大丽花_dahlia_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>8</v>
+      </c>
+      <c r="C31" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F31" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>9</v>
+      </c>
+      <c r="C37" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">349_千层金绿_Melaleuca bracteata
+（dyed orange）_Melaleuca bracteata F.Muell._1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="C40" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -670,7 +841,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>052510355815402551281057104</v>
+        <v>05251035581540255128105710426128553055103015184581410155580</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-10-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-24.xlsx
@@ -783,6 +783,9 @@
       <c r="C41" t="str">
         <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -841,7 +844,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>05251035581540255128105710426128553055103015184581410155580</v>
+        <v>052510355815402551281057104261285530551030151845814101555819</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-10-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -787,9 +787,90 @@
         <v>19</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>571_大飞燕浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>514_松虫草紫_scabiosa purple_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F46" t="str">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>10</v>
+      </c>
+      <c r="C47" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F47" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F48" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="C51" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -844,7 +925,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>052510355815402551281057104261285530551030151845814101555819</v>
+        <v>052510355815402551281057104261285530551030151845814101555819205105120182020100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-10-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-24.xlsx
@@ -867,6 +867,9 @@
         <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
 white_Trachymene Coerulea_1bunch</v>
       </c>
+      <c r="F51" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -925,7 +928,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>052510355815402551281057104261285530551030151845814101555819205105120182020100</v>
+        <v>052510355815402551281057104261285530551030151845814101555819205105120182020105</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-10-24.xlsx
+++ b/DateBase/orders/Nhat 48_2026-10-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L53"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -871,9 +871,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F52" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>11</v>
+      </c>
+      <c r="C53" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L53"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -928,7 +947,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>052510355815402551281057104261285530551030151845814101555819205105120182020105</v>
+        <v>0525103558154025512810571042612855305510301518458141015558192051051201820201052010</v>
       </c>
     </row>
   </sheetData>
